--- a/registros.xlsx
+++ b/registros.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,7 +923,7 @@
           <t>ANDREA CAROLINA TORRES NUÑEZ</t>
         </is>
       </c>
-      <c r="B17" s="3" t="n">
+      <c r="B17" s="2" t="n">
         <v>45888</v>
       </c>
       <c r="C17" t="inlineStr">
@@ -944,6 +944,336 @@
       <c r="F17" t="inlineStr">
         <is>
           <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>karen juliana cepeda garcia</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>karen juliana cepeda garcia</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>11:34</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>karen juliana cepeda garcia</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>karen juliana cepeda garcia</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>andrea carolina torres nunez</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>12:09</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>karen juliana cepeda garcia</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>12:11</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>karen juliana cepeda garcia</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>natalia carrillo hernandez</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>karen juliana cepeda garcia</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>fredy alexander calcetero pardo</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>fredy alexander calcetero pardo</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>45889</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Cita médica</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Con novedad</t>
         </is>
       </c>
     </row>

--- a/registros.xlsx
+++ b/registros.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,7 +1253,7 @@
           <t>fredy alexander calcetero pardo</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="2" t="n">
         <v>45889</v>
       </c>
       <c r="C28" t="inlineStr">
@@ -1274,6 +1274,66 @@
       <c r="F28" t="inlineStr">
         <is>
           <t>Con novedad</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>karen juliana cepeda garcia</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45890</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tarde</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>karen juliana cepeda garcia</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>45890</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Sin novedad</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Tarde</t>
         </is>
       </c>
     </row>
